--- a/model/genetikum_doublefalse_from_disease/evaluation.xlsx
+++ b/model/genetikum_doublefalse_from_disease/evaluation.xlsx
@@ -414,11 +414,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NDE1,ASPM,RAB3GAP2,RTTN,ADGRG1,ERCC1,TUBA8,SLC16A2,CIT,TBCK</t>
+          <t>NDE1,ASPM,TBCK,ACTG1,KATNB1,RTTN,GFM2,ERCC1,SLC9A6,GPSM2,WDR62,SLC16A2,ASNS,CIT,AIMP1,RAB3GAP2,DYNC1I2,PRUNE1,FRMD4A,ARX,RARS2,RAB18,PCLO,AP4E1,LARGE1,KIF14,ANKRD11,ADGRG1,WDR81,CASK</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>293</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3">
@@ -442,11 +442,11 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>PGAP3,ZNHIT3,EMC1,TCF4,ACTG1,UBE3A,ASPM,AHDC1,FRMD4A,ADGRG1</t>
+          <t>PGAP3,ASPM,TCF4,FRMD4A,ACTG1,ZNHIT3,DDX3X,AIMP1,DOCK7,RAC1,UBE3A,ADGRG1,AHDC1,TBCK,ARID1B,UNC80,EMC1,ADSL,PPP2R1A,TSEN54,POMGNT1,MAB21L1,MECP2,INPP5E,KATNB1,RAB18,ARID2,SMARCE1,ITPA,WDR62</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1109</v>
+        <v>703</v>
       </c>
     </row>
     <row r="4">
@@ -470,11 +470,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>PAX6,BMP4,FOXC1,OTX2,MAB21L2,FOXE3,HMGB3,ZSWIM6,HMX1,POMT2</t>
+          <t>MAB21L2,PITX2,TENM3,ARHGAP31,EFNB1,POMT2,POMT1,FKTN,FKRP,LARGE1,FOXC1,FGFR1,BMP4,FOXE3,PAX6,RBP4,OTX2,PAX2,SMO,ALDH1A3,SHH,RAX,ZSWIM6,ACTG1,SHH,HMX1,ATOH7,PXDN,SLC38A8,CENPF</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>310</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5">
@@ -498,11 +498,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ST3GAL3,KIF2A,WDR62,PAFAH1B1,CNPY3,ZNHIT3,POMT2,POMT1,FKTN,FKRP</t>
+          <t>PAFAH1B1,WDR62,GPSM2,PGAP3,POMT2,POMT1,FKTN,FKRP,LARGE1,POMT2,ST3GAL3,TUBG1,POMGNT1,TUBA8,B3GALNT2,ITPA,ASPM,TSEN54,CRADD,KATNB1,DOCK7,POMT1,ASNS,PIGP,AIMP1,FKRP,TUBA1A,KIF2A,DAG1,CRPPA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>292</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6">
@@ -526,11 +526,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>GJC2,PLP1,TWNK,TMEM240,VLDLR,SLC16A2,TTC19,PMPCA,SLC9A6,ELP2</t>
+          <t>GJC2,TWNK,PDHX,PLP1,MECP2,SLC18A2,PLA2G6,EARS2,GRID2,COASY,GRM1,AFG3L2,ATXN2,HTT,RAB11B,TUBB4A,SLC30A9,WDR45,ADGRG1,IREB2,AUH,PIEZO2,FOXG1,SLC6A3,DEGS1,POLR3B,VPS13A,SLC9A6,AIMP1,PANK2</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1489</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="7">
@@ -554,11 +554,11 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ADGRG1,ADSL,HTT,GJC2,VLDLR,MECP2,SLC16A2,PLP1,ELP2,CLN8</t>
+          <t>TWNK,GJC2,ADGRG1,HTT,MECP2,PLA2G6,GM2A,DEGS1,ADSL,GPAA1,PLP1,AIMP1,VPS11,TUBB4A,WARS2,PDHX,RARS2,FA2H,PMPCB,IREB2,TBCD,RAB11B,GRM1,TMEM106B,GRID2,BRAT1,FOXG1,FAM126A,KIF5A,POLR3B</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>224</v>
+        <v>243</v>
       </c>
     </row>
     <row r="8">
@@ -582,11 +582,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ANKRD11,ACTG1,KMT2A,MED12,ARID2,KANSL1,EFNB1,PCGF2,ACTB,ASXL1</t>
+          <t>KANSL1,ANKRD11,HNRNPK,KMT2A,ACTB,EFNB1,HSPA9,CILK1,PCGF2,PYCR1,MED12,PPP2R1A,ASXL1,RBM10,NFIX,ZEB2,PACS1,ACTG1,ABL1,CDC42,ARID2,AHDC1,EFTUD2,CTU2,RAF1,RIT1,TMCO1,C12ORF57,KIAA1109,OFD1</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1656</v>
+        <v>2158</v>
       </c>
     </row>
     <row r="9">
@@ -610,11 +610,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ZSWIM6,KMT2A,TCF4,ADSL,UNC80,ANKRD11,MECP2,DYRK1A,PGAP3,MAGEL2</t>
+          <t>TCF4,KANSL1,SHANK3,ZSWIM6,UNC80,UBE3A,STRADA,FOXG1,DOCK7,ARID2,MAGEL2,PIGV,ASPM,ANKRD11,ASXL3,KMT2A,EXT2,DDX3X,CERT1,PIGY,MECP2,ARNT2,KMT2E,AIMP1,WDR26,UBE2A,ZEB2,HNRNPH2,AHDC1,SLC6A8</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2381</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="10">
@@ -638,11 +638,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>SPG11,SPAST,GBA2,ABCD1,ZFYVE26,COASY,SPG7,TTC19,KIF5A,NIPA1</t>
+          <t>SPG11,COASY,GBA2,SPAST,PLP1,CYP7B1,KIF5A,NIPA1,RTN2,CACNA1G,ZFYVE26,KIF1A,AP5Z1,SACS,GJC2,ABCD1,SPG7,ARL6IP1,SPART,BSCL2,WASHC5,DDHD1,C19ORF12,FA2H,CAPN1,ALDH18A1,ATL1,REEP1,SPG21,ERLIN2</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>507</v>
+        <v>428</v>
       </c>
     </row>
     <row r="11">
@@ -666,11 +666,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ASPM,CNTNAP2,DDX3X,DPYS,ADSL,DEAF1,RAB39B,ELP2,CLN8,MECP2</t>
+          <t>ASPM,CNTNAP2,MECP2,ADGRG1,GM2A,WDR62,PAFAH1B1,RAB39B,AMT,GLDC,GCSH,RAC1,DEAF1,DDX3X,TCF4,FOXG1,GABBR2,PLA2G6,TWNK,UBE3A,MECP2,HERC2,DPYS,SLC9A6,ARID2,MECP2,VPS11,CLN3,WDR45,ADSL</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>90</v>
+        <v>219</v>
       </c>
     </row>
     <row r="12">
@@ -694,11 +694,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>B4GAT1,TUBA8,MPDZ,WDR62,LAMA1,POMK,ATN1,TUBGCP6,ARNT2,VPS11</t>
+          <t>MPDZ,TYR,MITF,TUBGCP6,VPS13B,POMK,ADGRG1,CRB1,SLC38A8,TYR,KIDINS220,CHMP1A,ATN1,ARX,TUBA8,HPS6,PEX16,PAX6,ASNS,SLC45A2,CCDC174,ARNT2,KIF14,CIT,KATNB1,CENPF,TMTC3,LAMA1,GPSM2,VPS11</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13">
@@ -722,7 +722,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>WNT10B,TP63,TP63,WNT7A,HOXD13,CDH3,PITX1,FBLN1,TP63,GDF3</t>
+          <t>WNT10B,TP63,TP63,CDH3,DLX5,WNT7A,PMP22,TP63,TP63,PMP22,PORCN,JPH1,GDAP1,HSPB1,WNT7A,HOXD13,IRF6,ATP6V1B2,GDF6,HOXD13,GDF5,PITX1,ROR2,EGR2,DNM2,RAB7A,LMBR1,INF2,LAMA3,LAMB3</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -750,11 +750,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LAMA1,ADGRG1,CRPPA,GPSM2,INPP5E,B4GAT1,TMEM216,POMT2,POMT1,FKTN</t>
+          <t>GPSM2,NSD1,ADGRG1,POMGNT1,LAMA1,POMT2,POMT1,FKTN,FKRP,LARGE1,LRP2,POMK,MPDZ,B4GAT1,INPP5E,DAG1,OPHN1,KIAA1109,CRPPA,POMT2,PIK3R2,RAC1,STRADA,RPGRIP1L,FKRP,TCF4,HSD17B4,C2CD3,CILK1,RAB11B</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>154</v>
+        <v>235</v>
       </c>
     </row>
     <row r="15">
@@ -778,11 +778,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ANKRD11,NECTIN1,TCOF1,FRAS1,RECQL4,EDNRA,KMT2D,KDM6A,FREM2,TWIST1</t>
+          <t>TWIST1,PIGL,ANKRD11,MYCN,EFTUD2,IL11RA,SMC3,PTPRF,KMT2A,TCOF1,EVC2,EVC,TBX15,BHLHA9,TWIST2,RBM10,EFNB1,IFT57,SF3B4,FGF3,NOG,FRAS1,EDNRA,FGFR3,FGFR2,FGF10,TWIST2,GRIP1,HOXD13,RIPK4</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>125</v>
+        <v>353</v>
       </c>
     </row>
     <row r="16">
@@ -806,11 +806,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CNTN1,LGI4,GLE1,ASCC1,ERGIC1,CNTNAP1,MUSK,GLE1,LMOD3,MYL1</t>
+          <t>GLE1,CNTN1,CNTNAP1,LGI4,SLC6A9,TRIP4,NUP88,GLE1,MYBPC1,ASCC1,MYH8,KLHL41,MTM1,KLHL40,TRIM2,CHRNA1,NEB,BICD2,ZC4H2,LMOD3,ACTA1,CDK5,TPM2,IGHMBP2,CNTNAP1,CEP55,CHRNG,MYL1,UBA1,CHRND</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17">
@@ -834,11 +834,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>MATN3,DYM,COL2A1,EXOC6B,TONSL,DYM,SLC26A2,SLC10A7,COL2A1,RAB33B</t>
+          <t>POP1,DYM,DYM,TRIP11,COL2A1,DDRGK1,TRPV4,TRAPPC2,SLC10A7,MATN3,LFNG,FN1,COL2A1,COMP,ACAN,EXOC6B,COL2A1,BGN,SLC26A2,RSPRY1,TRPV4,CANT1,TONSL,CANT1,RUNX2,IHH,TRPV4,SFRP4,EXTL3,NKX3-2</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18">
@@ -862,11 +862,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAB3GAP2,PC,SLC16A2,PHGDH,PGAP3,HSD17B10,ZNHIT3,EARS2,ITPA,RELN</t>
+          <t>PC,NDE1,ZNHIT3,PHGDH,ASPM,KATNB1,AIMP1,SUCLA2,KIF14,SLC16A2,WARS2,RAB18,FKRP,RTTN,VPS33B,ACTG1,GLYCTK,BOLA3,GFM2,ABAT,TMEM70,HMGCL,NDUFS4,DOCK6,PDHA1,TBC1D20,ADGRG1,ATPAF2,ITPA,TANGO2</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>750</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19">
@@ -890,11 +890,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ASPM,ARID2,ACTG1,KMT2A,ANKRD11,FRMD4A,ADSL,DYRK1A,HDAC8,EIF2S3</t>
+          <t>ASPM,ANKRD11,ARID2,DDX3X,KMT2A,EFTUD2,CDK10,TTI2,HERC2,FRMD4A,HDAC8,KANSL1,CSNK2A1,ACTG1,WDR62,KIF14,CERT1,ADSL,TCF4,ELP2,HS6ST2,WDR26,SLC6A17,EBF3,SHANK3,SMARCA2,WDR73,TRIO,RLIM,NSUN2</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>335</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20">
@@ -918,11 +918,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>KMT2A,ANKRD11,SOX11,TUBB,ALX4,ACTG1,GJA1,TBL1XR1,ARID2,EFNB1</t>
+          <t>ANKRD11,KMT2A,DLX4,ARID2,SOX11,SATB2,AHDC1,IL11RA,PCGF2,PPP2R1A,ALX4,EFNB1,PTPRF,SCARF2,BRF1,PTCH1,KAT6B,TWIST1,SMC3,MEIS2,IFT57,KANSL1,RBM10,RPS6KA3,GLI2,HNRNPK,ZIC2,SHANK3,BRAF,FRMD4A</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>456</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21">
@@ -946,7 +946,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>BLM,NF1,NF1,BRAF,MAP2K1,PTPN11,NF1,BRIP1,FANCG,SPRED1</t>
+          <t>BLM,NF1,NF1,BRAF,MAP2K1,PTPN11,BRIP1,NF1,SPRED1,FANCG,ANKRD11,KITLG,RAF1,PALB2,PMS2,MLH1,MSH2,MSH6,TSC1,BRAF,SLX4,RBBP8,BRCA2,BRAF,RIT1,RERE,FANCI,NBN,ERCC4,MTOR</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -974,11 +974,11 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ADGRG1,SOBP,SLC38A8,KIDINS220,TULP1,CRB1,FRMD7,SLC45A2,SALL2,TYR</t>
+          <t>SALL2,ADGRG1,GLRB,DNMBP,KIDINS220,SOBP,EMC1,GRID2,CHMP1A,SLC38A8,BLOC1S3,TENM3,CRB1,KIF21A,PHOX2A,TBC1D23,HMGB3,VPS13B,RPGRIP1,GTPBP2,TCF4,INPP5E,NEUROD2,MAG,TYR,MITF,ATAD3A,CRB1,ACOX1,SCN8A</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1124</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="23">
@@ -1002,11 +1002,11 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ZSWIM6,UNC80,PGAP3,ASPM,ADSL,DDX3X,ZNHIT3,FRMD4A,PIGP,NACC1</t>
+          <t>ASPM,DOCK7,ASXL3,UNC80,DDX3X,TCF4,CERT1,FOXG1,PURA,ZNHIT3,ASNS,TRAPPC9,WDR26,RAB11B,PGAP3,ACTG1,ADSL,AIMP1,ZSWIM6,PIGA,PIGV,VPS11,PCLO,SMARCE1,AHDC1,GTPBP2,STRADA,NEXMIF,SHANK3,ANKRD11</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>421</v>
+        <v>474</v>
       </c>
     </row>
     <row r="24">
@@ -1030,11 +1030,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>PIGV,GDNF,EDN3,PIGO,SOX10,EDN3,EDNRB,MNX1,EDNRB,RET</t>
+          <t>PIGV,EDNRB,EDN3,EDN3,PIGO,RET,KIT,SNAI2,EDNRB,PAX3,MNX1,ACTG2,SOX10,GDNF,HPSE2,EDNRB,ZEB2,MKKS,PAX3,PHOX2B,MSX2,ALX4,SOX10,MITF,SALL1,KMT2D,KDM6A,MITF,PGAP3,DDX59</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1058,11 +1058,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SMARCA2,ANKRD11,FRMD4A,KMT2A,TCF4,DYRK1A,CERT1,CDK10,GATAD2B,ARID1B</t>
+          <t>ANKRD11,SMARCA2,TCF4,KMT2A,FRMD4A,TBL1XR1,SHANK3,ARID1B,HERC2,KANSL1,SMC3,ACTG1,GATAD2B,ASPM,SMARCE1,UBE2A,DYRK1A,CKAP2L,PACS1,HSPA9,ZEB2,KMT2D,KDM6A,MBD5,PTPRF,TBCK,CERT1,EHMT1,SOX11,TWIST2</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LARGE1,BIN1,WDR62,NEB,FKRP,RTTN,BICD2,LAMA2,FKRP,DAG1</t>
+          <t>LARGE1,ACTA1,TUBB2B,TRIM2,FKRP,FKRP,WDR62,NEB,FKTN,CDK5,TPM2,ZC4H2,SLC12A6,CRPPA,CHKB,BIN1,DYNC1I2,TRIP4,MEGF10,PLEC,BICD2,POMT1,KATNB1,CCDC174,LMNA,MYMK,POMK,KY,GFM2,POMT2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1114,11 +1114,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>INPP5E,TMEM216,TMEM67,CEP290,NPHP1,RPGRIP1L,AHI1,LAMA1,ADGRG1,MRE11</t>
+          <t>INPP5E,NPHP1,TMEM216,CEP290,TMEM67,AHI1,RPGRIP1L,SUFU,LAMA1,CPLANE1,ADGRG1,ITPR1,WDR81,ATXN2,KIAA0586,GRM1,XRCC1,GRID2,CEP41,ARMC9,CC2D2A,RPGRIP1L,TMEM67,VLDLR,POLR3B,CSPP1,TMEM231,CEP120,SLC30A9,PIBF1</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>114</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28">
@@ -1142,11 +1142,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>ZSWIM6,ACTG1,CERT1,CDK10,ARID2,PGAP3,UNC80,AHDC1,ZNHIT3,CDK5</t>
+          <t>GTPBP2,NSD1,CERT1,ANKRD11,PIGV,DOCK7,OTUD6B,PGAP3,AHDC1,UNC80,ZNHIT3,SHANK3,EBF3,ZSWIM6,WDR73,ALG9,DOCK6,PDHX,TBCK,PCLO,DDX3X,ARID2,PYCR1,TRAPPC9,TRMT1,TCF4,EMC1,CCDC88A,PIGP,ACTG1</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>235</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29">
@@ -1170,11 +1170,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>UNC80,ZSWIM6,SYT1,RNF113A,SLC16A2,SNX14,FBXL4,FRMD4A,ELP2,PARS2</t>
+          <t>UNC80,ZSWIM6,PDHX,GTPBP2,PIGA,CDC42,TBCK,NSD1,PIGS,AHDC1,ALG9,FRMD4A,ANKRD11,RAF1,HACE1,RAB11B,DOCK7,SNX14,CCDC47,KMT2E,PCLO,CERT1,EXT2,BRAF,ZNHIT3,HNRNPH2,CSF1R,ASNS,CCDC22,DOCK6</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>23</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30">
@@ -1198,11 +1198,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>GJC2,RAB39B,CSF1R,L2HGDH,WDR45,RNASET2,WDR62,GRN,MECP2,MECP2</t>
+          <t>SRPX2,FAM126A,HEPACAM,RNASET2,HEPACAM,GJC2,MLC1,HEPACAM,VPS13D,COASY,TSC1,TSC2,MTOR,CSF1R,PAFAH1B1,WDR62,MECP2,MECP2,TWNK,SCN1B,RAB39B,HTRA1,VPS13A,GPSM2,CHMP2B,DNAJC12,PRNP,KATNB1,GJC2,GM2A</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>636</v>
+        <v>418</v>
       </c>
     </row>
     <row r="31">
@@ -1226,11 +1226,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>KMT2A,ANKRD11,PGAP3,HDAC8,LAS1L,MAGEL2,MKRN3,SNORD116-1,SNORD115-1,NDN</t>
+          <t>ANKRD11,TCF4,MKRN3,SNORD116-1,SNORD115-1,NDN,IPW,PWRN1,MAGEL2,PWAR1,MKRN3-AS1,HERC2,NPAP1,SNRPN,HDAC8,KMT2A,MAGEL2,LAS1L,UBE3A,ADSL,PGAP3,TBL1XR1,UBE2A,TRAPPC9,HERC2,EBF3,ASPM,ADNP,ZSWIM6,UNC80</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32">
@@ -1254,11 +1254,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>NSD1,HERC1,TBC1D7,PIK3R2,SETD2,ARID2,EED,DNMT3A,EZH2,NFIX</t>
+          <t>NSD1,HERC1,EED,SHANK3,STRADA,DNMT3A,EZH2,OPHN1,TBC1D7,AHDC1,SETD2,PIK3R2,MECP2,OFD1,ZSWIM6,TCF20,MTOR,KMT2E,KIAA1109,ARID2,RAF1,ANKRD11,RAC1,BRAF,CSF1R,EXT2,NFIX,KPTN,SUFU,ALKBH8</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>431</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33">
@@ -1282,11 +1282,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ANKRD11,SMS,VPS13B,EFNB1,KMT2A,ATP6V1E1,ACTG1,CDK10,PCGF2,SCARF2</t>
+          <t>ANKRD11,KMT2A,EFNB1,ASXL1,TCF4,ARID2,HNRNPK,RIT1,BRAF,PPP2R1A,SCARF2,PACS1,RAF1,AHDC1,IL11RA,C12ORF57,PCGF2,BRAF,MAP2K1,PTPN11,SOX5,NSD1,PPP2CA,SOS1,CCDC22,EED,KRAS,ACTG1,SMS,TBL1XR1</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>325</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34">
@@ -1310,11 +1310,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>TCOF1,ACTG1,TWIST1,EFTUD2,EDNRA,ALX3,GLI2,TXNL4A,ZSWIM6,SHH</t>
+          <t>EFTUD2,PTCH1,TWIST1,SHH,GLI2,ACTG1,TCOF1,TGIF1,ARID2,ZSWIM6,SIX3,ZIC2,ALX3,SMC3,ALX1,TXNL4A,ASPM,FGFR2,KMT2A,CDH11,ANKRD11,PLCB4,FRAS1,FGFR1,EDNRA,PIGL,ACTB,TUBB,EFNB1,HNRNPK</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>98</v>
+        <v>174</v>
       </c>
     </row>
     <row r="35">
@@ -1338,11 +1338,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>KMT2A,ANKRD11,DYRK1A,HDAC8,CDK10,ACTG1,ASPM,STAG2,DYNC1I2,ADSL</t>
+          <t>ANKRD11,KMT2A,ASPM,HDAC8,DYRK1A,CDK10,KAT6B,UNC80,SMARCA2,EFTUD2,TRRAP,STAG2,WDR4,PIGY,SMC3,SIN3A,BPTF,ACTG1,TCF4,ADSL,TRMT1,SHANK3,EXT2,HERC2,ARID2,FLCN,CERT1,WDR73,OTUD6B,ATR</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1420</v>
+        <v>963</v>
       </c>
     </row>
     <row r="36">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ANKRD11,KMT2A,ACTG1,HDAC8,FGD1,SMARCA2,EFNB1,CDK10,XYLT1,TBL1XR1</t>
+          <t>ANKRD11,KMT2A,EFNB1,ASPM,IFT57,FGD1,ACTG1,RPS6KA3,CCDC22,XYLT1,SMARCA2,BPTF,TBL1XR1,SMC1A,BRAF,MAP2K1,PTPN11,MED12,SIN3A,SMS,MYO18B,RPL10,CKAP2L,RSPRY1,ARID2,HUWE1,HDAC8,FRMD4A,SMC3,FBXO11</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -1394,11 +1394,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ANKRD11,ACTG1,BRAF,MAP2K1,PTPN11,EFNB1,MEIS2,KMT2A,KDM6A,ARID2</t>
+          <t>ANKRD11,EFNB1,ACTG1,KMT2A,EFTUD2,BRAF,MAP2K1,PTPN11,SMC3,SIN3A,CTCF,ARID2,TWIST1,MEIS2,KANSL1,TBL1XR1,PGAP3,ACTB,INTU,CHD4,TRAF7,RBM10,ASPM,ZNF148,PACS1,HNRNPK,ZEB2,KDM6A,PPP2R1A,KAT6B</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>80</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -1422,11 +1422,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RSPO2,COL11A1,TRIP11,TBX15,INTU,HSPG2,SCARF2,COL2A1,SLC35D1,TAPT1</t>
+          <t>TBX15,TRIP11,COL11A1,EFNB1,HSPG2,RSPO2,INTU,COL2A1,TAPT1,GPC6,BMPER,LBR,SLC35D1,PTH1R,FLNA,FAM20C,IL11RA,WNT7A,CHUK,SCARF2,EVC2,EVC,IFT43,FGFR2,POR,ALG9,FLNB,SOX9,CEP120,RUNX2</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>122</v>
+        <v>164</v>
       </c>
     </row>
     <row r="39">
@@ -1450,11 +1450,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ACTG1,ANKRD11,KMT2A,DHCR7,COL11A1,PGAP3,SMG9,HDAC8,CENPJ,ADSL</t>
+          <t>ANKRD11,KMT2A,PGAP3,ACTG1,ALG9,DHCR7,SIN3A,COL11A1,ATP6V0A2,ORC1,FRMD4A,ACTB,ASXL1,NIPBL,PEX19,CRIPT,MTOR,ATP6V0A2,HDAC8,KAT6B,ASPM,PEX2,SMC1A,PEX5,GLIS3,SMARCA2,NALCN,SCARF2,SMC3,OBSL1</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
@@ -1478,11 +1478,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>IHH,SLC35D1,COL2A1,NPR2,FGFR3,NKX3-2,MATN3,BGN,ACAN,MMP13</t>
+          <t>DYM,NPR2,NKX3-2,IHH,COL2A1,FGFR3,SLC35D1,TRIP11,ACAN,BGN,DYM,HDAC6,COL10A1,RMRP,DDRGK1,SLC10A7,FGFR3,POP1,GPX4,MATN3,FGFR3,RUNX2,TONSL,COL2A1,EXOC6B,TRPV4,POC1A,FGFR3,IFT43,XYLT1</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>486</v>
+        <v>335</v>
       </c>
     </row>
     <row r="41">
@@ -1506,11 +1506,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>TBX15,DHCR7,ACTG1,FAT4,COL11A1,DCHS1,KMT2A,C2CD3,CILK1,EFNB1</t>
+          <t>KMT2A,DHCR7,SLC25A24,KAT6B,EFNB1,ACTB,FAT4,ALG9,LTBP4,CILK1,ASXL1,COL11A1,ORC1,OFD1,PEX13,ATP6V0A2,ATP6V0A2,HNRNPK,ATRX,PTPRF,MTOR,PGAP3,HSPA9,ANKRD11,KANSL1,TCF4,RBM10,SCARF2,AHDC1,PEX1</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>519</v>
+        <v>755</v>
       </c>
     </row>
     <row r="42">
@@ -1534,11 +1534,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PSMB8,IGHMBP2,DST,TRIM2,PEX5,ASCC1,AGL,MPV17,ALG1,TRMT5</t>
+          <t>TRMT5,SMPD1,AGL,TRIM2,PSMB8,TRIP4,POLG2,TMEM165,PEX5,HSPG2,COG7,POLG,INPP5K,FASTKD2,TACO1,COX20,SCO1,COX8A,COX10,TRNN,COX14,COX6B1,PET100,TRNS1,COA8,NEU1,PNPLA2,ATP5F1D,PLAA,MPV17</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1768</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="43">
@@ -1562,11 +1562,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>PAFAH1B1,GPSM2,ADGRG1,B4GAT1,LAMB1,TSEN54,WDR62,ZNHIT3,DENND5A,GJC2</t>
+          <t>PAFAH1B1,GPSM2,ADGRG1,LAMB1,NDE1,ASPM,CSF1R,CIT,ABAT,B4GAT1,WDR62,KATNB1,TMTC3,AIMP1,ASNS,CRADD,L1CAM,DENND5A,TUBA1A,AP4M1,EML1,TSEN54,PIGA,MPDZ,KIAA1109,PDHX,TSEN54,TOE1,ZNHIT3,TBCK</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="44">
@@ -1590,11 +1590,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>ASPM,UNC80,ASNS,PAFAH1B1,SLC16A2,RAB3GAP2,WDR62,NDE1,CIT,ADSL</t>
+          <t>ASPM,ASNS,AIMP1,CIT,CSF1R,KATNB1,TBCK,ZNHIT3,NDE1,UNC80,WDR62,PAFAH1B1,ADGRG1,WDR73,PRUNE1,RAB18,DOCK6,DOCK7,DYNC1I2,CCDC88A,RAB11B,RARS2,UFC1,IER3IP1,RTTN,FOXG1,GFM2,PCLO,TBCD,RNF113A</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>539</v>
+        <v>874</v>
       </c>
     </row>
     <row r="45">
@@ -1618,11 +1618,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ARID2,ANKRD11,ZSWIM6,KMT2A,NSD1,ASPM,XYLT1,FRMD4A,BRAF,MAP2K1</t>
+          <t>ANKRD11,ASPM,NSD1,ARID2,KMT2A,AHDC1,KMT2E,RPS6KA3,EED,STRADA,CDK10,ZSWIM6,RAF1,SHANK3,EBF3,BRAF,MAP2K1,PTPN11,OTUD6B,MAGEL2,EZH2,CWC27,HS6ST2,CBL,HERC1,HERC2,ACTG1,RIT1,CCDC22,XYLT1</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
     <row r="46">
@@ -1646,11 +1646,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NECTIN1,POC1A,WDR35,HOXD13,MSX1,CHSY1,CDH3,EVC2,EVC,TP63</t>
+          <t>IFT57,EFNB1,BHLHA9,CTSK,RUNX2,ANKRD11,TP63,WDR35,CHSY1,CTNND1,TWIST2,HOXD13,PORCN,POC1A,EVC2,EVC,ROR2,PTPRF,TP63,IL11RA,TCTN3,HEPHL1,NECTIN4,CDH3,TP63,TBL1XR1,RIPK4,ATP6V1B2,XYLT1,NECTIN1</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
